--- a/results/breakdown/nitrous oxide production, AON real, green ammonia.xlsx
+++ b/results/breakdown/nitrous oxide production, AON real, green ammonia.xlsx
@@ -429,7 +429,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.914302275241587</v>
+        <v>1.914302275241586</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -446,7 +446,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.7883644498883717</v>
+        <v>0.7883644498883733</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -463,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0006792469803216145</v>
+        <v>0.0006792469803216111</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -480,7 +480,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.04466307302218787</v>
+        <v>0.04466307302218789</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -497,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.007301011413137552</v>
+        <v>0.007301011413137562</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>1.069151705754485</v>
+        <v>1.069151705754486</v>
       </c>
       <c r="E7">
         <v>1</v>
